--- a/Terrain_Clutter_RF_Recommendation_Filled_Unique.xlsx
+++ b/Terrain_Clutter_RF_Recommendation_Filled_Unique.xlsx
@@ -629,22 +629,22 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells only)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Flat ground gives near-LOS propagation and street-canyon waveguiding, so with ISD of 250–500 m the main beam lands well beyond the serving area. Downtilt source 2° (target EDT 6–10°) to pull beam-centre inside ~0.7×ISD; co-sector +1° keeps inter-sector overlap balanced and avoids HO ping-pong; tier-1 cells boresight-facing the source +1° to remove the shared overlap zone. Validate TA (≥90% samples within ~0.5 km), SINR/CQI and RSRP ≥ -100 dBm. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Dense-urban weak coverage is mostly building penetration/indoor loss, not tilt; every degree of uptilt adds interference to many close neighbours. Only a 1° uptilt on source (do not go below EDT ~4°); co-sector and tier-1 untouched to protect SINR. If the gap persists, prefer power/small cell/indoor solution over further uptilt.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Flat ground gives near-LOS propagation and street-canyon waveguiding, so with ISD of 250–500 m the main beam lands well beyond the serving area. Downtilt source 2° (target EDT 6–10°) to pull beam-centre inside ~0.7×ISD; co-sector +1° keeps inter-sector overlap balanced and avoids HO ping-pong; tier-1 cells boresight-facing the source +1° to remove the shared overlap zone. Validate TA (≥90% samples within ~0.5 km), SINR/CQI and RSRP ≥ -100 dBm. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Dense-urban weak coverage is mostly building penetration/indoor loss, not tilt; every degree of uptilt adds interference to many close neighbours. Only a 1° uptilt on source (do not go below EDT ~4°); co-sector and tier-1 untouched to protect SINR. If the gap persists, prefer power/small cell/indoor solution over further uptilt.</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). ISD 500–1000 m on flat terrain: overshoot is common because there is no terrain to stop the signal. Downtilt source 2° (target EDT 5–8°), co-sector +1° to keep intra-site boundary aligned. Tier-1 kept as-is and monitored; tilt them only if overlap with source still &gt;30% after the change (avoid creating holes by tilting both sides). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (cell facing gap only) – Gap typically sits mid-way between sites. Close it jointly with small steps: source -1° and the one tier-1 cell facing the gap -1°, rather than a large uptilt on one cell. Co-sector unchanged to avoid new overlap. Keep EDT ≥ 3–4°.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). ISD 500–1000 m on flat terrain: overshoot is common because there is no terrain to stop the signal. Downtilt source 2° (target EDT 5–8°), co-sector +1° to keep intra-site boundary aligned. Tier-1 kept as-is and monitored; tilt them only if overlap with source still &gt;30% after the change (avoid creating holes by tilting both sides). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – cell facing gap only) – Gap typically sits mid-way between sites. Close it jointly with small steps: source -1° and the one tier-1 cell facing the gap -1°, rather than a large uptilt on one cell. Co-sector unchanged to avoid new overlap. Keep EDT ≥ 3–4°.</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Low clutter + flat terrain = long reach (ISD 1–2 km). Source downtilt 2° (target EDT 3–6°) is sufficient to cut far-end spill; co-sector and tier-1 normally do not need change because suburban overlap is lower. Monitor TA and neighbour-cell RSRP after change. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (facing cells only) – Suburban is moderately coverage-limited and interference is low, so a 2° uptilt on source is acceptable; facing tier-1 -1° to close gap from both sides. Co-sector unchanged. Ensure upper 3 dB beam edge stays at/below horizon to prevent overshoot.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Low clutter + flat terrain = long reach (ISD 1–2 km). Source downtilt 2° (target EDT 3–6°) is sufficient to cut far-end spill; co-sector and tier-1 normally do not need change because suburban overlap is lower. Monitor TA and neighbour-cell RSRP after change. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – facing cells only) – Suburban is moderately coverage-limited and interference is low, so a 2° uptilt on source is acceptable; facing tier-1 -1° to close gap from both sides. Co-sector unchanged. Ensure upper 3 dB beam edge stays at/below horizon to prevent overshoot.</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>-2° Uptilt</t>
+          <t>-2° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>-1° Uptilt</t>
+          <t>-1° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Rural is coverage-limited and interference is low, so maximise footprint: uptilt source 2° (target EDT 0–2°) and co-sector 1° for contiguous coverage. Tier-1 unchanged. Do not tilt above horizon (upper beam edge at 0°) – energy into the sky is wasted. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Rural is coverage-limited and interference is low, so maximise footprint: uptilt source 2° (target EDT 0–2°) and co-sector 1° for contiguous coverage. Tier-1 unchanged. Do not tilt above horizon (upper beam edge at 0°) – energy into the sky is wasted. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>-2° Uptilt</t>
+          <t>-2° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-1° Uptilt</t>
+          <t>-1° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Canopy loss drives the gap; uptilting source 2° and co-sector 1° lifts the beam to graze over treetops and extend reach. Tier-1 unchanged. If RSRP still weak, consider low band (700/800/900 MHz) layer or antenna height increase rather than more uptilt. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Canopy loss drives the gap; uptilting source 2° and co-sector 1° lifts the beam to graze over treetops and extend reach. Tier-1 unchanged. If RSRP still weak, consider low band (700/800/900 MHz) layer or antenna height increase rather than more uptilt. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (cells facing open area)</t>
+          <t>+1° Downtilt (Reduce Coverage – cells facing open area)</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Open areas (water bodies, airports, large parks, highways) have no clutter loss – signal travels very far, and over water ducting/reflection causes extreme overshoot. Strong downtilt 3° on source (target EDT 6–10°), co-sector +1°, and tier-1 cells facing the open area +1° to contain spill. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Low-interference open area (e.g. highway/rail corridor): uptilt source 2° to extend coverage along the corridor; co-sector and tier-1 unchanged. Align azimuth with the road/rail and verify HO sequence along the route by drive test.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Open areas (water bodies, airports, large parks, highways) have no clutter loss – signal travels very far, and over water ducting/reflection causes extreme overshoot. Strong downtilt 3° on source (target EDT 6–10°), co-sector +1°, and tier-1 cells facing the open area +1° to contain spill. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Low-interference open area (e.g. highway/rail corridor): uptilt source 2° to extend coverage along the corridor; co-sector and tier-1 unchanged. Align azimuth with the road/rail and verify HO sequence along the route by drive test.</t>
         </is>
       </c>
     </row>
@@ -851,22 +851,22 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells only)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Gentle undulations put crests in LOS and troughs in shadow; sites on crests overshoot onto the next crest. Downtilt source 2° (target EDT 6–10°), co-sector +1° for balanced boundary, facing tier-1 +1°. Check the source site's height vs surrounding ground – elevated sites need extra tilt. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Weak spots usually sit in troughs/terrain shadow; uptilt does not fill shadow and adds interference. Limit to 1° uptilt on source, co-sector/tier-1 unchanged. Residual holes: small cell or neighbour azimuth tuning.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Gentle undulations put crests in LOS and troughs in shadow; sites on crests overshoot onto the next crest. Downtilt source 2° (target EDT 6–10°), co-sector +1° for balanced boundary, facing tier-1 +1°. Check the source site's height vs surrounding ground – elevated sites need extra tilt. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Weak spots usually sit in troughs/terrain shadow; uptilt does not fill shadow and adds interference. Limit to 1° uptilt on source, co-sector/tier-1 unchanged. Residual holes: small cell or neighbour azimuth tuning.</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Crest-to-crest LOS creates island coverage far from site. Downtilt source 2° (target EDT 5–8°), co-sector +1°. Tier-1 monitored and adjusted only if overlap remains, to avoid creating trough holes. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (cell facing gap only) – Gap often lies in a dip between two sites; use small joint steps: source -1° and the tier-1 cell facing the dip -1°. Co-sector unchanged. Re-check terrain profile – if the dip is in shadow from both, tilt will not help.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Crest-to-crest LOS creates island coverage far from site. Downtilt source 2° (target EDT 5–8°), co-sector +1°. Tier-1 monitored and adjusted only if overlap remains, to avoid creating trough holes. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – cell facing gap only) – Gap often lies in a dip between two sites; use small joint steps: source -1° and the tier-1 cell facing the dip -1°. Co-sector unchanged. Re-check terrain profile – if the dip is in shadow from both, tilt will not help.</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Low clutter + undulating terrain: overshoot on crests. Source downtilt 2° (target EDT 3–6°). Co-sector and tier-1 unchanged; monitor neighbour RSRP/TA after change. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (facing cells only) – Moderate interference and gentle terrain allow 2° uptilt on source to reach far slopes; facing tier-1 -1° to close gap jointly. Co-sector unchanged. Keep upper beam edge at horizon.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Low clutter + undulating terrain: overshoot on crests. Source downtilt 2° (target EDT 3–6°). Co-sector and tier-1 unchanged; monitor neighbour RSRP/TA after change. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – facing cells only) – Moderate interference and gentle terrain allow 2° uptilt on source to reach far slopes; facing tier-1 -1° to close gap jointly. Co-sector unchanged. Keep upper beam edge at horizon.</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>-2° Uptilt</t>
+          <t>-2° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>-1° Uptilt</t>
+          <t>-1° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Maximise footprint: source -2°, co-sector -1° (target EDT 0–2°). Undulating ground gives partial LOS so uptilt is effective here. Tier-1 unchanged. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Maximise footprint: source -2°, co-sector -1° (target EDT 0–2°). Undulating ground gives partial LOS so uptilt is effective here. Tier-1 unchanged. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>-1° Uptilt</t>
+          <t>-1° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>-1° Uptilt (facing cells only)</t>
+          <t>-1° Uptilt (Increase Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Foliage + rolling terrain: uptilt source 1° and facing tier-1 1° to graze canopy and fill between-site gap. Avoid large uptilt – canopy blocks anyway; consider low band if insufficient. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Foliage + rolling terrain: uptilt source 1° and facing tier-1 1° to graze canopy and fill between-site gap. Avoid large uptilt – canopy blocks anyway; consider low band if insufficient. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Open land/water between undulations gives clear LOS and reflections. Downtilt source 2°, co-sector +1° to contain spill (target EDT 5–8°). Tier-1 unchanged, monitor. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Open area with low interference; 1° uptilt on source to extend reach along corridor/open land. Co-sector/tier-1 unchanged; verify by drive test.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Open land/water between undulations gives clear LOS and reflections. Downtilt source 2°, co-sector +1° to contain spill (target EDT 5–8°). Tier-1 unchanged, monitor. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Open area with low interference; 1° uptilt on source to extend reach along corridor/open land. Co-sector/tier-1 unchanged; verify by drive test.</t>
         </is>
       </c>
     </row>
@@ -1073,22 +1073,22 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells only)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Sites on high ground fire across valleys onto opposite hills – classic overshoot/pilot pollution. Apply downtilt in two steps (+2° then +1°) on source (target EDT 8–12°); co-sector +1° and facing tier-1 +1°. If EDT range is exhausted, add mechanical tilt. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (only if gap is in LOS), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – In hilly terrain most gaps are terrain shadow behind hills, which uptilt cannot fix. First confirm with terrain profile: uptilt 1° only if gap is LOS from source, else let the tier-1 neighbour that has LOS uptilt 1°. Co-sector unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Sites on high ground fire across valleys onto opposite hills – classic overshoot/pilot pollution. Apply downtilt in two steps (+2° then +1°) on source (target EDT 8–12°); co-sector +1° and facing tier-1 +1°. If EDT range is exhausted, add mechanical tilt. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage – only if gap is in LOS), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – In hilly terrain most gaps are terrain shadow behind hills, which uptilt cannot fix. First confirm with terrain profile: uptilt 1° only if gap is LOS from source, else let the tier-1 neighbour that has LOS uptilt 1°. Co-sector unchanged.</t>
         </is>
       </c>
     </row>
@@ -1110,22 +1110,22 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells only)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Elevated sites see far hills; strong downtilt 3° on source (target EDT 7–10°), co-sector +1°, facing tier-1 +1° to break cross-valley overlap. Validate with TA distribution and neighbour RSRP. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Gap often behind hill crest: uptilt source 1° only for LOS portion, and use the neighbour with LOS to the gap (-1°). Co-sector unchanged. Persistent shadow → new site/repeater.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Elevated sites see far hills; strong downtilt 3° on source (target EDT 7–10°), co-sector +1°, facing tier-1 +1° to break cross-valley overlap. Validate with TA distribution and neighbour RSRP. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Gap often behind hill crest: uptilt source 1° only for LOS portion, and use the neighbour with LOS to the gap (-1°). Co-sector unchanged. Persistent shadow → new site/repeater.</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Hilltop suburban sites overshoot into adjacent valleys. Downtilt source 2° (target EDT 5–8°), co-sector +1°. Tier-1 monitored. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Use small steps; shadowing dominates. Source -1°, LOS tier-1 -1°. Co-sector unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Hilltop suburban sites overshoot into adjacent valleys. Downtilt source 2° (target EDT 5–8°), co-sector +1°. Tier-1 monitored. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Use small steps; shadowing dominates. Source -1°, LOS tier-1 -1°. Co-sector unchanged.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Hilltop rural sites serve distant valleys (very high TA) and interfere with far sites. Downtilt source 2° (target EDT 3–6°). Co-sector/tier-1 unchanged to protect rural coverage. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Gap at cell edge in LOS can be helped by 1° uptilt; gaps in valley shadow need the neighbour with LOS (-1°). Note: if gap is on valley floor close to the hilltop site, it is under the beam – downtilt instead of uptilt.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Hilltop rural sites serve distant valleys (very high TA) and interfere with far sites. Downtilt source 2° (target EDT 3–6°). Co-sector/tier-1 unchanged to protect rural coverage. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Gap at cell edge in LOS can be helped by 1° uptilt; gaps in valley shadow need the neighbour with LOS (-1°). Note: if gap is on valley floor close to the hilltop site, it is under the beam – downtilt instead of uptilt.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Elevated site above forest clears canopy toward far hills. Downtilt source 2° (target EDT 3–6°). Co-sector/tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Forest + hill shadow: small 1° uptilt on source and LOS neighbour. Co-sector unchanged. Low band/antenna height more effective than tilt here.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Elevated site above forest clears canopy toward far hills. Downtilt source 2° (target EDT 3–6°). Co-sector/tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Forest + hill shadow: small 1° uptilt on source and LOS neighbour. Co-sector unchanged. Low band/antenna height more effective than tilt here.</t>
         </is>
       </c>
     </row>
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells only)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Lakes/reservoirs/open land between hills: strong reflection and LOS overshoot. Downtilt source 3°, co-sector +1°, facing tier-1 +1° (target EDT 6–10°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Highway/open area through hills: 1° uptilt on source if LOS; align azimuth along road. Co-sector/tier-1 unchanged; verify HO along route.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Lakes/reservoirs/open land between hills: strong reflection and LOS overshoot. Downtilt source 3°, co-sector +1°, facing tier-1 +1° (target EDT 6–10°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Highway/open area through hills: 1° uptilt on source if LOS; align azimuth along road. Co-sector/tier-1 unchanged; verify HO along route.</t>
         </is>
       </c>
     </row>
@@ -1295,22 +1295,22 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>+4° Downtilt</t>
+          <t>+4° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt (facing cells)</t>
+          <t>+2° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Towns in mountain areas have sites on slopes hundreds of metres above the served area – effective antenna height is huge, so overshoot is severe. Source +4° in steps (target EDT 10–14°, combine with mechanical tilt if EDT range is exhausted), co-sector +2°, facing tier-1 +2°. Check vertical beamwidth (~6–8°) so upper beam edge lands within cell. | If weak coverage/coverage gap is the issue instead: Source 0° No Change (fix via azimuth/power), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour across valley) – Gaps are terrain shadow; uptilting a high site only increases interference across the valley. Keep source tilt, fix with azimuth/power or a new low-height site; let a neighbour with LOS across the valley uptilt 1°.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Towns in mountain areas have sites on slopes hundreds of metres above the served area – effective antenna height is huge, so overshoot is severe. Source +4° in steps (target EDT 10–14°, combine with mechanical tilt if EDT range is exhausted), co-sector +2°, facing tier-1 +2°. Check vertical beamwidth (~6–8°) so upper beam edge lands within cell. | If weak coverage/coverage gap is the issue instead: Source 0° No Change (fix via azimuth/power), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour across valley) – Gaps are terrain shadow; uptilting a high site only increases interference across the valley. Keep source tilt, fix with azimuth/power or a new low-height site; let a neighbour with LOS across the valley uptilt 1°.</t>
         </is>
       </c>
     </row>
@@ -1332,22 +1332,22 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). High effective height → cross-valley overshoot. Source +3° (target EDT 8–12°), co-sector +2°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (only if gap is in LOS), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Shadowing dominates; uptilt only for LOS gaps. Use LOS tier-1 -1°. Co-sector unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). High effective height → cross-valley overshoot. Source +3° (target EDT 8–12°), co-sector +2°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage – only if gap is in LOS), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Shadowing dominates; uptilt only for LOS gaps. Use LOS tier-1 -1°. Co-sector unchanged.</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Settlements on slopes/valley sides; high sites overshoot. Source +3° (target EDT 7–10°), co-sector +1°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Small steps only; source -1° and LOS tier-1 -1°. Co-sector unchanged; residual shadow → infill site.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Settlements on slopes/valley sides; high sites overshoot. Source +3° (target EDT 7–10°), co-sector +1°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Small steps only; source -1° and LOS tier-1 -1°. Co-sector unchanged; residual shadow → infill site.</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Alpine meadows/open slopes: signal propagates tens of km across valleys, causing very high TA and far interference. Source +3° (target EDT 5–8°), co-sector +1°. Tier-1 unchanged (sparse rural sites). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Coverage-limited but terrain-blocked: 1° uptilt only for LOS gaps at far edge. If gap is on the valley floor below the site, it is under the main lobe – downtilt instead. Co-sector/tier-1 unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Alpine meadows/open slopes: signal propagates tens of km across valleys, causing very high TA and far interference. Source +3° (target EDT 5–8°), co-sector +1°. Tier-1 unchanged (sparse rural sites). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Coverage-limited but terrain-blocked: 1° uptilt only for LOS gaps at far edge. If gap is on the valley floor below the site, it is under the main lobe – downtilt instead. Co-sector/tier-1 unchanged.</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Forested mountain slopes: overshoot across valleys over canopy. Source +2°, co-sector +1° (target EDT 5–8°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (LOS neighbour) – Forest + terrain shadow: small 1° uptilt on source and LOS neighbour; prefer low band / additional site.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Forested mountain slopes: overshoot across valleys over canopy. Source +2°, co-sector +1° (target EDT 5–8°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – LOS neighbour) – Forest + terrain shadow: small 1° uptilt on source and LOS neighbour; prefer low band / additional site.</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Glaciers, lakes, ski slopes: open LOS and snow/water reflection extend reach dramatically. Source +3°, co-sector +1°, facing tier-1 +1° (target EDT 7–10°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Mountain pass/highway: uptilt source 1° and align azimuth along the road; co-sector/tier-1 unchanged. Validate by drive test (HO sequence, no ping-pong).</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Glaciers, lakes, ski slopes: open LOS and snow/water reflection extend reach dramatically. Source +3°, co-sector +1°, facing tier-1 +1° (target EDT 7–10°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Mountain pass/highway: uptilt source 1° and align azimuth along the road; co-sector/tier-1 unchanged. Validate by drive test (HO sequence, no ping-pong).</t>
         </is>
       </c>
     </row>
@@ -1517,22 +1517,22 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (cells along valley axis)</t>
+          <t>+1° Downtilt (Reduce Coverage – cells along valley axis)</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Valley slopes contain the signal laterally but it channels along the valley axis and reflects off slopes (multipath, interference). Downtilt source 2° (target EDT 6–10°), co-sector +1°, tier-1 along the valley axis +1°. Watch for temperature-inversion ducting in basins. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Dense urban valley floor: weak coverage is indoor/penetration loss. Only 1° uptilt on source; co-sector/tier-1 unchanged to protect SINR.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Valley slopes contain the signal laterally but it channels along the valley axis and reflects off slopes (multipath, interference). Downtilt source 2° (target EDT 6–10°), co-sector +1°, tier-1 along the valley axis +1°. Watch for temperature-inversion ducting in basins. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Dense urban valley floor: weak coverage is indoor/penetration loss. Only 1° uptilt on source; co-sector/tier-1 unchanged to protect SINR.</t>
         </is>
       </c>
     </row>
@@ -1554,22 +1554,22 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (cells along valley axis)</t>
+          <t>+1° Downtilt (Reduce Coverage – cells along valley axis)</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Along-valley overshoot is the main issue. Source +2° (target EDT 5–8°), co-sector +1°, along-axis tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (cell facing gap only) – Residences climbing the slopes sit above the beam; source -1° and facing neighbour -1° to lift coverage up the slopes. Co-sector unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Along-valley overshoot is the main issue. Source +2° (target EDT 5–8°), co-sector +1°, along-axis tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – cell facing gap only) – Residences climbing the slopes sit above the beam; source -1° and facing neighbour -1° to lift coverage up the slopes. Co-sector unchanged.</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Suburbs on slopes overlook the basin – sites there overshoot across the basin. Source +2° (target EDT 4–7°), co-sector +1°. Tier-1 monitored. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (facing cells only) – Users on rising slopes are above the antenna's horizontal plane, so uptilt is effective: source -2°, facing tier-1 -1°. Co-sector unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Suburbs on slopes overlook the basin – sites there overshoot across the basin. Source +2° (target EDT 4–7°), co-sector +1°. Tier-1 monitored. | If weak coverage/coverage gap is the issue instead: Source -2° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – facing cells only) – Users on rising slopes are above the antenna's horizontal plane, so uptilt is effective: source -2°, facing tier-1 -1°. Co-sector unchanged.</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>-2° Uptilt</t>
+          <t>-2° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>-1° Uptilt</t>
+          <t>-1° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Coverage-limited; slopes rise away from site so uptilt helps: source -2°, co-sector -1° (target EDT 0–2°). Tier-1 unchanged. | If overshooting/interference is observed instead (high TA, low SINR): Source +2° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Coverage-limited; slopes rise away from site so uptilt helps: source -2°, co-sector -1° (target EDT 0–2°). Tier-1 unchanged. | If overshooting/interference is observed instead (high TA, low SINR): Source +2° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>-2° Uptilt</t>
+          <t>-2° Uptilt (Increase Coverage)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>-1° Uptilt (facing cells only)</t>
+          <t>-1° Uptilt (Increase Coverage – facing cells only)</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Forested slopes higher than site: source -2° and facing tier-1 -1° to reach up-slope users. Co-sector unchanged; consider low band. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
+          <t>Dominant issue: Coverage-limited environment (weak RSRP / coverage gaps). Forested slopes higher than site: source -2° and facing tier-1 -1° to reach up-slope users. Co-sector unchanged; consider low band. | If overshooting/interference is observed instead (high TA, low SINR): Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor).</t>
         </is>
       </c>
     </row>
@@ -1702,22 +1702,22 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). River/lake on valley floor: water reflection + along-valley channelling. Source +2°, co-sector +1°, facing tier-1 +1° (target EDT 5–8°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Valley highway/rail: 1° uptilt and azimuth aligned to route; co-sector/tier-1 unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). River/lake on valley floor: water reflection + along-valley channelling. Source +2°, co-sector +1°, facing tier-1 +1° (target EDT 5–8°). | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Valley highway/rail: 1° uptilt and azimuth aligned to route; co-sector/tier-1 unchanged.</t>
         </is>
       </c>
     </row>
@@ -1739,22 +1739,22 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>+4° Downtilt</t>
+          <t>+4° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Site on ridge/high building sees the whole city – extreme overshoot and pilot pollution. Source +4° in steps (target EDT ≥10–14°; add mechanical tilt if EDT range exhausted), co-sector +2°, facing tier-1 +1°. Verify upper 3 dB beam edge falls inside intended cell radius. | If weak coverage/coverage gap is the issue instead: Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – From a ridge, weak coverage near the site in the city below is because the main lobe passes over it ('under-the-beam'). Downtilt (not uptilt) source +1° to bring the main lobe onto the served area. Co-sector/tier-1 unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Site on ridge/high building sees the whole city – extreme overshoot and pilot pollution. Source +4° in steps (target EDT ≥10–14°; add mechanical tilt if EDT range exhausted), co-sector +2°, facing tier-1 +1°. Verify upper 3 dB beam edge falls inside intended cell radius. | If weak coverage/coverage gap is the issue instead: Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – From a ridge, weak coverage near the site in the city below is because the main lobe passes over it ('under-the-beam'). Downtilt (not uptilt) source +1° to bring the main lobe onto the served area. Co-sector/tier-1 unchanged.</t>
         </is>
       </c>
     </row>
@@ -1776,22 +1776,22 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>+4° Downtilt</t>
+          <t>+4° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). High effective height → very long LOS reach. Source +4° (target EDT 10–12°), co-sector +2°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source +1° Downtilt, Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (cell covering far edge) – Near-site gap is under-the-beam → downtilt source +1°. Far-edge gaps should be served by the lower tier-1 neighbour (-1°), not by uptilting the ridge site.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). High effective height → very long LOS reach. Source +4° (target EDT 10–12°), co-sector +2°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source +1° Downtilt (Reduce Coverage), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – cell covering far edge) – Near-site gap is under-the-beam → downtilt source +1°. Far-edge gaps should be served by the lower tier-1 neighbour (-1°), not by uptilting the ridge site.</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge site over low clutter: overshoot many km. Source +3° (target EDT 7–10°), co-sector +1°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source 0° No Change (Monitor), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (cell covering far edge) – Do not uptilt a ridge site – it floods the area with interference. Keep source tilt; let the lower tier-1 neighbour uptilt 1° to fill far-edge gap.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge site over low clutter: overshoot many km. Source +3° (target EDT 7–10°), co-sector +1°, facing tier-1 +1°. | If weak coverage/coverage gap is the issue instead: Source 0° No Change (Monitor), Co-sector 0° No Change (Monitor), Tier-1 -1° Uptilt (Increase Coverage – cell covering far edge) – Do not uptilt a ridge site – it floods the area with interference. Keep source tilt; let the lower tier-1 neighbour uptilt 1° to fill far-edge gap.</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>+3° Downtilt</t>
+          <t>+3° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge over open rural: coverage can reach 20–30 km, hurting distant sites. Source +3°, co-sector +1° (target EDT 4–7°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Rural is coverage-limited; a cautious 1° uptilt on source for far-edge gaps. If gap is close to site, it is under the beam – downtilt instead. Co-sector/tier-1 unchanged.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge over open rural: coverage can reach 20–30 km, hurting distant sites. Source +3°, co-sector +1° (target EDT 4–7°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Rural is coverage-limited; a cautious 1° uptilt on source for far-edge gaps. If gap is close to site, it is under the beam – downtilt instead. Co-sector/tier-1 unchanged.</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt</t>
+          <t>+1° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge clears canopy and overshoots. Source +2°, co-sector +1° (target EDT 4–7°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt, Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Forest loss dominates; small 1° uptilt on source. Co-sector/tier-1 unchanged; consider low band.</t>
+          <t>Dominant issue: Interference-limited / overshooting environment (high TA, low SINR, pilot pollution). Ridge clears canopy and overshoots. Source +2°, co-sector +1° (target EDT 4–7°). Tier-1 unchanged. | If weak coverage/coverage gap is the issue instead: Source -1° Uptilt (Increase Coverage), Co-sector 0° No Change (Monitor), Tier-1 0° No Change (Monitor) – Forest loss dominates; small 1° uptilt on source. Co-sector/tier-1 unchanged; consider low band.</t>
         </is>
       </c>
     </row>
@@ -1924,17 +1924,17 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>+4° Downtilt</t>
+          <t>+4° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>+2° Downtilt</t>
+          <t>+2° Downtilt (Reduce Coverage)</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>+1° Downtilt (facing cells)</t>
+          <t>+1° Downtilt (Reduce Coverage – facing cells)</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
